--- a/data/trans_camb/P16A13-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,55</t>
+          <t>-0,35; 2,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,62</t>
+          <t>-0,81; 1,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,8</t>
+          <t>-0,73; 7,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 0,53</t>
+          <t>-2,52; 0,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,11</t>
+          <t>-2,29; 1,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,4</t>
+          <t>-2,79; 0,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,08</t>
+          <t>-0,99; 1,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,9</t>
+          <t>-1,18; 0,91</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,19</t>
+          <t>-1,23; 3,11</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-91,02; 101,17</t>
+          <t>-89,04; 99,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,02; 130,56</t>
+          <t>-87,9; 132,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 177,03</t>
+          <t>-100,0; 124,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-64,09; 151,12</t>
+          <t>-63,94; 155,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,55; 145,77</t>
+          <t>-76,47; 139,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-97,65; 524,69</t>
+          <t>-97,83; 548,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,16</t>
+          <t>-0,97; 2,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,6</t>
+          <t>-1,44; 1,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,26</t>
+          <t>-1,79; 1,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,61</t>
+          <t>-0,45; 2,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,97</t>
+          <t>-0,81; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,5</t>
+          <t>-1,43; 1,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,86</t>
+          <t>-0,29; 1,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,27</t>
+          <t>-0,74; 1,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,86</t>
+          <t>-1,14; 0,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 231,04</t>
+          <t>-47,04; 200,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-61,8; 155,38</t>
+          <t>-63,68; 183,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,74; 135,66</t>
+          <t>-81,79; 142,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,91; 437,54</t>
+          <t>-35,04; 389,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 303,27</t>
+          <t>-50,27; 305,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,96; 236,63</t>
+          <t>-79,88; 279,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 187,36</t>
+          <t>-18,07; 188,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,88; 128,42</t>
+          <t>-39,83; 136,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 92,99</t>
+          <t>-64,31; 80,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,14</t>
+          <t>-1,7; 1,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,0</t>
+          <t>-2,08; 1,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,15</t>
+          <t>-2,16; 1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,95</t>
+          <t>-0,35; 3,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,4</t>
+          <t>-1,59; 1,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,54</t>
+          <t>-0,4; 2,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,0</t>
+          <t>-0,41; 2,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,74</t>
+          <t>-1,44; 0,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,34</t>
+          <t>-0,7; 1,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,85; 133,64</t>
+          <t>-52,08; 129,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 80,1</t>
+          <t>-65,75; 89,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,97; 82,97</t>
+          <t>-69,5; 106,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 247,51</t>
+          <t>-18,32; 252,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,54; 117,64</t>
+          <t>-64,4; 114,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 231,03</t>
+          <t>-19,42; 207,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 128,36</t>
+          <t>-16,96; 140,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,92; 47,25</t>
+          <t>-54,2; 48,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 86,94</t>
+          <t>-28,85; 89,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,15</t>
+          <t>0,07; 5,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,61</t>
+          <t>-2,5; 1,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,19</t>
+          <t>-1,57; 4,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,9</t>
+          <t>-0,64; 4,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,08</t>
+          <t>-4,5; -0,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,69</t>
+          <t>-1,65; 2,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,99</t>
+          <t>0,49; 4,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,03</t>
+          <t>-2,77; -0,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,76</t>
+          <t>-0,87; 2,83</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 313,08</t>
+          <t>-0,66; 338,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,12; 111,51</t>
+          <t>-66,59; 103,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 226,53</t>
+          <t>-42,96; 241,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 172,26</t>
+          <t>-13,5; 179,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,26; 2,35</t>
+          <t>-79,74; -4,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 99,1</t>
+          <t>-30,12; 100,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,49; 158,55</t>
+          <t>8,01; 153,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 2,33</t>
+          <t>-67,13; -0,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 103,45</t>
+          <t>-22,1; 104,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,97</t>
+          <t>-3,01; 2,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,26</t>
+          <t>-1,38; 4,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 7,08</t>
+          <t>1,71; 7,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 5,16</t>
+          <t>-1,97; 5,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,7</t>
+          <t>-1,22; 5,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,39</t>
+          <t>1,51; 7,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,91</t>
+          <t>-1,61; 2,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 4,08</t>
+          <t>-0,55; 3,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,54</t>
+          <t>2,23; 6,39</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 83,07</t>
+          <t>-58,84; 81,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,93; 152,16</t>
+          <t>-31,25; 158,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11,53; 280,99</t>
+          <t>32,47; 286,06</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-26,13; 132,2</t>
+          <t>-27,91; 114,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 140,8</t>
+          <t>-16,77; 140,77</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,86; 199,86</t>
+          <t>17,45; 186,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 74,58</t>
+          <t>-27,86; 73,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 107,57</t>
+          <t>-10,45; 107,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>40,52; 178,38</t>
+          <t>35,8; 178,42</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 7,21</t>
+          <t>-1,02; 7,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 4,15</t>
+          <t>-2,93; 4,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,3</t>
+          <t>3,9; 11,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,69</t>
+          <t>-0,7; 7,73</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 2,39</t>
+          <t>-4,68; 2,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 9,34</t>
+          <t>-5,41; 8,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,63</t>
+          <t>0,46; 6,49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,38</t>
+          <t>-2,98; 2,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 8,52</t>
+          <t>-1,38; 8,86</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 278,87</t>
+          <t>-19,48; 293,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 158,49</t>
+          <t>-46,49; 158,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53,94; 421,72</t>
+          <t>48,52; 461,74</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 132,05</t>
+          <t>-8,11; 141,87</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 43,37</t>
+          <t>-49,27; 57,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-48,38; 144,36</t>
+          <t>-57,23; 134,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,19; 141,35</t>
+          <t>5,06; 140,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-38,04; 49,5</t>
+          <t>-40,5; 47,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 164,5</t>
+          <t>-9,81; 179,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,52</t>
+          <t>-0,35; 11,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 3,83</t>
+          <t>-5,27; 3,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,96; 16,87</t>
+          <t>6,93; 17,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,22</t>
+          <t>-0,07; 8,39</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,26</t>
+          <t>-0,54; 8,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,77; 23,85</t>
+          <t>15,33; 23,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,17</t>
+          <t>1,26; 7,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,79</t>
+          <t>-1,04; 5,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,7; 19,91</t>
+          <t>13,72; 19,94</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 203,71</t>
+          <t>-5,23; 228,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 83,57</t>
+          <t>-50,55; 78,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>63,52; 343,82</t>
+          <t>55,06; 367,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 173,5</t>
+          <t>-2,53; 180,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 179,31</t>
+          <t>-8,16; 173,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>151,85; 509,96</t>
+          <t>143,73; 515,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,85; 141,78</t>
+          <t>12,41; 145,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,64; 101,54</t>
+          <t>-12,98; 100,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>142,73; 364,7</t>
+          <t>145,75; 378,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,47</t>
+          <t>0,49; 2,4</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,15</t>
+          <t>-0,51; 1,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,48</t>
+          <t>1,83; 4,4</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,78</t>
+          <t>0,69; 2,79</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,39</t>
+          <t>-0,44; 1,48</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,28</t>
+          <t>2,74; 5,29</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,27</t>
+          <t>1,01; 2,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,05</t>
+          <t>-0,21; 0,99</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,64</t>
+          <t>2,81; 4,59</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>21,4; 109,54</t>
+          <t>14,96; 110,7</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 47,88</t>
+          <t>-17,3; 52,04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>69,24; 203,3</t>
+          <t>61,79; 199,35</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,56; 86,16</t>
+          <t>17,18; 89,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 43,52</t>
+          <t>-11,1; 47,18</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>69,34; 164,69</t>
+          <t>73,61; 169,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,56; 81,8</t>
+          <t>28,91; 83,67</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 37,34</t>
+          <t>-6,53; 34,88</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>87,23; 167,78</t>
+          <t>84,02; 158,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A13-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>-1,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,61</t>
+          <t>-0,15; 2,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,8</t>
+          <t>-0,8; 1,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 7,51</t>
+          <t>-0,61; 3,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,5</t>
+          <t>-2,42; 0,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,14</t>
+          <t>-2,26; 0,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,35</t>
+          <t>-2,67; 0,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 1,05</t>
+          <t>-0,87; 1,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,91</t>
+          <t>-1,19; 0,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,11</t>
+          <t>-1,21; 1,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199,16%</t>
+          <t>128,41%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-71,28%</t>
+          <t>-71,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-6,51%</t>
+          <t>-25,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-76,15; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-89,04; 99,09</t>
+          <t>-89,91; 85,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-87,9; 132,77</t>
+          <t>-89,64; 114,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,37</t>
+          <t>-100,0; 170,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 155,84</t>
+          <t>-60,24; 169,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,47; 139,94</t>
+          <t>-75,53; 143,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-97,83; 548,58</t>
+          <t>-87,83; 195,37</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,16</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 2,1</t>
+          <t>-0,83; 2,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,58</t>
+          <t>-1,39; 1,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,31</t>
+          <t>-1,63; 1,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,53</t>
+          <t>-0,52; 2,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,88</t>
+          <t>-0,82; 1,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,38</t>
+          <t>-0,95; 1,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,85</t>
+          <t>-0,31; 1,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,32</t>
+          <t>-0,76; 1,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,78</t>
+          <t>-0,82; 1,37</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-22,3%</t>
+          <t>-9,8%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,26%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-16,69%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-47,04; 200,55</t>
+          <t>-39,42; 221,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,68; 183,67</t>
+          <t>-62,33; 142,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,79; 142,59</t>
+          <t>-77,03; 158,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 389,19</t>
+          <t>-39,7; 415,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 305,1</t>
+          <t>-55,76; 318,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,88; 279,35</t>
+          <t>-65,23; 310,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 188,36</t>
+          <t>-21,51; 182,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,83; 136,54</t>
+          <t>-43,1; 119,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 80,3</t>
+          <t>-46,65; 152,27</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,08</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,89</t>
+          <t>-1,44; 2,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,22</t>
+          <t>-2,08; 1,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,28</t>
+          <t>-2,44; 0,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 3,1</t>
+          <t>-0,22; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,24</t>
+          <t>-1,63; 1,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,48</t>
+          <t>-0,49; 2,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 2,1</t>
+          <t>-0,39; 2,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,7</t>
+          <t>-1,46; 0,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,43</t>
+          <t>-0,97; 1,22</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-21,34%</t>
+          <t>-32,16%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,08; 129,6</t>
+          <t>-47,26; 123,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,75; 89,98</t>
+          <t>-66,89; 80,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,5; 106,75</t>
+          <t>-74,37; 53,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 252,39</t>
+          <t>-20,19; 258,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 114,54</t>
+          <t>-65,03; 121,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 207,47</t>
+          <t>-23,33; 219,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 140,08</t>
+          <t>-15,38; 132,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 48,26</t>
+          <t>-56,08; 42,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 89,19</t>
+          <t>-36,29; 75,47</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>2,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 5,01</t>
+          <t>0,43; 5,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,36</t>
+          <t>-2,37; 1,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,45</t>
+          <t>1,26; 6,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,98</t>
+          <t>-0,59; 4,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,38</t>
+          <t>-4,36; -0,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,61</t>
+          <t>-1,62; 2,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,14</t>
+          <t>0,54; 4,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; -0,07</t>
+          <t>-2,78; -0,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,83</t>
+          <t>0,47; 3,75</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>138,1%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 338,67</t>
+          <t>3,26; 365,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,59; 103,56</t>
+          <t>-62,04; 104,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 241,89</t>
+          <t>15,53; 375,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 179,52</t>
+          <t>-14,08; 162,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-79,74; -4,67</t>
+          <t>-79,82; -8,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 100,95</t>
+          <t>-28,71; 103,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,01; 153,04</t>
+          <t>9,88; 157,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,13; -0,6</t>
+          <t>-65,09; 4,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-22,1; 104,67</t>
+          <t>8,69; 151,9</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,45</t>
+          <t>3,98</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,13</t>
+          <t>-2,95; 2,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 4,08</t>
+          <t>-1,53; 4,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,22</t>
+          <t>1,19; 6,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,31</t>
+          <t>-1,66; 5,07</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,98</t>
+          <t>-1,36; 5,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,37</t>
+          <t>1,4; 6,95</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,75</t>
+          <t>-1,58; 2,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,97</t>
+          <t>-0,42; 4,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,39</t>
+          <t>1,98; 6,0</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114,4%</t>
+          <t>102,31%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 81,66</t>
+          <t>-58,44; 95,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 158,45</t>
+          <t>-32,94; 177,6</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32,47; 286,06</t>
+          <t>17,51; 252,72</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 114,38</t>
+          <t>-23,71; 119,28</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 140,77</t>
+          <t>-19,92; 128,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,45; 186,42</t>
+          <t>14,59; 172,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 73,51</t>
+          <t>-28,09; 70,18</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 107,49</t>
+          <t>-6,75; 111,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,8; 178,42</t>
+          <t>30,15; 156,64</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,32</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>7,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>7,39</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 7,4</t>
+          <t>-0,68; 7,59</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,04</t>
+          <t>-2,74; 4,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,9; 11,13</t>
+          <t>3,43; 10,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 7,73</t>
+          <t>-0,54; 7,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,97</t>
+          <t>-4,51; 2,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 8,9</t>
+          <t>4,05; 11,24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,49</t>
+          <t>0,33; 6,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,19</t>
+          <t>-2,68; 2,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 8,86</t>
+          <t>4,64; 9,63</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>185,76%</t>
+          <t>171,62%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>101,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>123,27%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 293,65</t>
+          <t>-18,72; 266,91</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-46,49; 158,79</t>
+          <t>-45,42; 159,09</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>48,52; 461,74</t>
+          <t>45,3; 454,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 141,87</t>
+          <t>-8,18; 140,93</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-49,27; 57,95</t>
+          <t>-50,58; 52,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 134,89</t>
+          <t>39,85; 216,56</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>5,06; 140,56</t>
+          <t>4,52; 132,31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-40,5; 47,44</t>
+          <t>-38,95; 48,73</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 179,05</t>
+          <t>59,35; 205,83</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,37</t>
+          <t>11,82</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,93</t>
+          <t>19,33</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,92</t>
+          <t>16,33</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 11,48</t>
+          <t>0,14; 10,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 3,82</t>
+          <t>-4,72; 4,39</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,93; 17,01</t>
+          <t>6,45; 16,8</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 8,39</t>
+          <t>-0,55; 8,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 8,73</t>
+          <t>-0,38; 8,68</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,33; 23,97</t>
+          <t>15,1; 23,31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,87</t>
+          <t>0,68; 8,01</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,62</t>
+          <t>-1,37; 5,49</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,72; 19,94</t>
+          <t>12,71; 19,36</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>162,52%</t>
+          <t>155,23%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>286,48%</t>
+          <t>277,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>234,65%</t>
+          <t>226,45%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 228,77</t>
+          <t>-1,17; 198,15</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 78,64</t>
+          <t>-48,55; 86,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>55,06; 367,01</t>
+          <t>58,0; 338,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 180,42</t>
+          <t>-7,52; 181,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 173,6</t>
+          <t>-6,79; 178,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>143,73; 515,85</t>
+          <t>145,31; 493,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,41; 145,12</t>
+          <t>7,07; 146,15</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 100,42</t>
+          <t>-15,11; 98,59</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>145,75; 378,56</t>
+          <t>134,35; 376,08</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>4,21</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,4</t>
+          <t>0,56; 2,32</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,15</t>
+          <t>-0,56; 1,09</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,4</t>
+          <t>2,66; 4,57</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,79</t>
+          <t>0,73; 2,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,48</t>
+          <t>-0,54; 1,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,29</t>
+          <t>3,83; 5,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,36</t>
+          <t>0,93; 2,31</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,99</t>
+          <t>-0,25; 0,99</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,59</t>
+          <t>3,53; 4,86</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>127,61%</t>
+          <t>136,02%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>117,89%</t>
+          <t>133,06%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>122,29%</t>
+          <t>134,71%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>14,96; 110,7</t>
+          <t>18,95; 101,56</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 52,04</t>
+          <t>-18,65; 47,66</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>61,79; 199,35</t>
+          <t>85,67; 201,42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>17,18; 89,73</t>
+          <t>16,06; 87,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 47,18</t>
+          <t>-13,82; 42,96</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>73,61; 169,91</t>
+          <t>93,52; 180,65</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,91; 83,67</t>
+          <t>26,45; 81,36</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 34,88</t>
+          <t>-7,89; 34,46</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>84,02; 158,33</t>
+          <t>103,95; 172,45</t>
         </is>
       </c>
     </row>
